--- a/CW_Outreaches/CW_outreach_merged.xlsx
+++ b/CW_Outreaches/CW_outreach_merged.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studium\X_Masterarbeit\Data\Master_Thesis\CW_Outreaches\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE50D608-0D1D-4C1C-91A0-3084E607F26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFA49AE-92EF-4B62-8B0D-D9B795A7BBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A3FB61B1-149E-455F-9115-958C77EC7E3F}"/>
   </bookViews>
@@ -740,9 +740,6 @@
     <t>Freiburg</t>
   </si>
   <si>
-    <t>KiKa television show</t>
-  </si>
-  <si>
     <t>Temporary river and stream meeting in Nottingham</t>
   </si>
   <si>
@@ -822,6 +819,9 @@
   </si>
   <si>
     <t>United States of America</t>
+  </si>
+  <si>
+    <t>KiKA television show</t>
   </si>
 </sst>
 </file>
@@ -865,10 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -879,13 +876,8 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1220,47 +1212,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA67A863-4EEC-4E14-9073-BBC2EA727455}">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="8"/>
-    <col min="4" max="4" width="18" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="110.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+      <c r="A2" s="1">
         <v>43846</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>185</v>
+      <c r="D2" t="s">
+        <v>184</v>
       </c>
       <c r="E2" t="s">
         <v>57</v>
@@ -1270,38 +1261,38 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+      <c r="A3" s="1">
         <v>43880</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="A4" s="1">
         <v>43888</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="1">
         <v>43895</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F5" t="s">
@@ -1309,10 +1300,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="A6" s="1">
         <v>43896</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F6" t="s">
@@ -1320,30 +1311,30 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="A7" s="1">
         <v>43908</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+      <c r="A8" s="1">
         <v>43948</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" t="s">
         <v>52</v>
       </c>
       <c r="E8" t="s">
@@ -1354,10 +1345,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+      <c r="A9" s="1">
         <v>43952</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F9" t="s">
@@ -1365,24 +1356,24 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+      <c r="A10" s="1">
         <v>43973</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
+      <c r="A11" s="1">
         <v>43979</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F11" t="s">
@@ -1390,24 +1381,24 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+      <c r="A12" s="1">
         <v>44089</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+      <c r="A13" s="1">
         <v>44104</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F13" t="s">
@@ -1415,44 +1406,44 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
+      <c r="A14" s="1">
         <v>44138</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+      <c r="A15" s="1">
         <v>44154</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+      <c r="A16" s="1">
         <v>44166</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" t="s">
         <v>52</v>
       </c>
       <c r="E16" t="s">
@@ -1463,10 +1454,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+      <c r="A17" s="1">
         <v>44194</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F17" t="s">
@@ -1474,24 +1465,24 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="A18" s="1">
         <v>44210</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
+      <c r="A19" s="1">
         <v>44271</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F19" t="s">
@@ -1499,10 +1490,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
+      <c r="A20" s="1">
         <v>44273</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F20" t="s">
@@ -1510,38 +1501,38 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
+      <c r="A21" s="1">
         <v>44274</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
+      <c r="A22" s="1">
         <v>44274</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
+      <c r="A23" s="1">
         <v>44296</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
@@ -1549,10 +1540,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
+      <c r="A24" s="1">
         <v>44303</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F24" t="s">
@@ -1560,24 +1551,24 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
+      <c r="A25" s="1">
         <v>44315</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
+      <c r="A26" s="1">
         <v>44316</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F26" t="s">
@@ -1585,36 +1576,36 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
+      <c r="A27" s="1">
         <v>44323</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>181</v>
+      <c r="D27" t="s">
+        <v>180</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
+      <c r="A28" s="1">
         <v>44334</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" t="s">
         <v>26</v>
       </c>
       <c r="E28" t="s">
@@ -1625,17 +1616,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+      <c r="A29" s="1">
         <v>44336</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C29" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>182</v>
+      <c r="D29" t="s">
+        <v>181</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -1645,38 +1636,38 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
+      <c r="A30" s="1">
         <v>44338</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F30" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
+      <c r="A31" s="1">
         <v>44362</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
+      <c r="A32" s="1">
         <v>44365</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F32" t="s">
@@ -1684,16 +1675,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
+      <c r="A33" s="1">
         <v>44371</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" t="s">
         <v>35</v>
       </c>
       <c r="E33" t="s">
@@ -1704,10 +1695,10 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
+      <c r="A34" s="1">
         <v>44372</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F34" t="s">
@@ -1715,10 +1706,10 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
+      <c r="A35" s="1">
         <v>44376</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F35" t="s">
@@ -1726,17 +1717,17 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
+      <c r="A36" s="1">
         <v>44398</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
       </c>
       <c r="E36" t="s">
         <v>40</v>
@@ -1746,10 +1737,10 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
+      <c r="A37" s="1">
         <v>44410</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E37" t="s">
@@ -1760,38 +1751,38 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
+      <c r="A38" s="1">
         <v>44442</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
+      <c r="A39" s="1">
         <v>44448</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F39" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
+      <c r="A40" s="1">
         <v>44470</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F40" t="s">
@@ -1799,38 +1790,38 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
+      <c r="A41" s="1">
         <v>44502</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F41" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
+      <c r="A42" s="1">
         <v>44503</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F42" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
+      <c r="A43" s="1">
         <v>44511</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="4" t="s">
         <v>162</v>
       </c>
       <c r="F43" t="s">
@@ -1838,17 +1829,17 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
+      <c r="A44" s="1">
         <v>44518</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>190</v>
+      <c r="D44" t="s">
+        <v>189</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -1858,16 +1849,16 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
+      <c r="A45" s="1">
         <v>44520</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C45" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" t="s">
         <v>52</v>
       </c>
       <c r="E45" t="s">
@@ -1878,30 +1869,30 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
+      <c r="A46" s="1">
         <v>44537</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F46" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
+      <c r="A47" s="1">
         <v>44538</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C47" t="s">
         <v>163</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" t="s">
         <v>163</v>
       </c>
       <c r="E47" t="s">
@@ -1912,1461 +1903,1397 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
+      <c r="A48" s="1">
         <v>44597</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
+      <c r="B48" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F48" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
+      <c r="A49" s="1">
         <v>44626</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="B49" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
+      <c r="A50" s="1">
         <v>44636</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="B50" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
         <v>36</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
+      <c r="A51" s="1">
         <v>44650</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="B51" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>44650</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>44652</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>44679</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" t="s">
+        <v>179</v>
+      </c>
+      <c r="F54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>44679</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>44684</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" t="s">
+        <v>179</v>
+      </c>
+      <c r="F56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>44685</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>44692</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" t="s">
+        <v>179</v>
+      </c>
+      <c r="F58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>44704</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>44704</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>44707</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>44723</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E62" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>44782</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>44805</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E64" t="s">
+        <v>179</v>
+      </c>
+      <c r="F64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>44808</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" t="s">
+        <v>179</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>44812</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>44825</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" t="s">
+        <v>179</v>
+      </c>
+      <c r="F67" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>44834</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E68" t="s">
+        <v>179</v>
+      </c>
+      <c r="F68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>44846</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E69" t="s">
+        <v>179</v>
+      </c>
+      <c r="F69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>44846</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F70" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>44862</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E71" t="s">
+        <v>179</v>
+      </c>
+      <c r="F71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>44869</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72" t="s">
+        <v>179</v>
+      </c>
+      <c r="F72" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>44886</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E73" t="s">
+        <v>179</v>
+      </c>
+      <c r="F73" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>44908</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" t="s">
+        <v>52</v>
+      </c>
+      <c r="E74" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>44936</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" t="s">
+        <v>40</v>
+      </c>
+      <c r="F75" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>44945</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" t="s">
+        <v>176</v>
+      </c>
+      <c r="D76" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" t="s">
+        <v>89</v>
+      </c>
+      <c r="F76" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>44952</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>44965</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E78" t="s">
+        <v>179</v>
+      </c>
+      <c r="F78" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>44966</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E79" t="s">
+        <v>179</v>
+      </c>
+      <c r="F79" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>44967</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E80" t="s">
+        <v>179</v>
+      </c>
+      <c r="F80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>44995</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E81" t="s">
+        <v>191</v>
+      </c>
+      <c r="F81" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45000</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E82" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45006</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" t="s">
+        <v>118</v>
+      </c>
+      <c r="E83" t="s">
+        <v>57</v>
+      </c>
+      <c r="F83" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45013</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" t="s">
+        <v>57</v>
+      </c>
+      <c r="F84" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45014</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E85" t="s">
+        <v>179</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45041</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F86" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45042</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+      <c r="D87" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" t="s">
+        <v>91</v>
+      </c>
+      <c r="F87" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45056</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>45087</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E89" t="s">
+        <v>179</v>
+      </c>
+      <c r="F89" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>45106</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F90" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>45114</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F91" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>45195</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C92" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" t="s">
+        <v>187</v>
+      </c>
+      <c r="E92" t="s">
+        <v>57</v>
+      </c>
+      <c r="F92" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>45209</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F93" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>45224</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C94" t="s">
+        <v>87</v>
+      </c>
+      <c r="D94" t="s">
+        <v>87</v>
+      </c>
+      <c r="E94" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>45231</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E95" t="s">
+        <v>179</v>
+      </c>
+      <c r="F95" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45244</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C96" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" t="s">
+        <v>186</v>
+      </c>
+      <c r="E96" t="s">
+        <v>57</v>
+      </c>
+      <c r="F96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45248</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E97" t="s">
+        <v>179</v>
+      </c>
+      <c r="F97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45258</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C98" t="s">
+        <v>52</v>
+      </c>
+      <c r="D98" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45272</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F99" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45273</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E100" t="s">
+        <v>179</v>
+      </c>
+      <c r="F100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45354</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C101" t="s">
+        <v>87</v>
+      </c>
+      <c r="D101" t="s">
+        <v>87</v>
+      </c>
+      <c r="E101" t="s">
+        <v>40</v>
+      </c>
+      <c r="F101" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45371</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C102" t="s">
+        <v>118</v>
+      </c>
+      <c r="D102" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" t="s">
+        <v>57</v>
+      </c>
+      <c r="F102" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45375</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E103" t="s">
+        <v>57</v>
+      </c>
+      <c r="F103" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45375</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E104" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45375</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45366</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E106" t="s">
+        <v>179</v>
+      </c>
+      <c r="F106" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45363</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E107" t="s">
+        <v>179</v>
+      </c>
+      <c r="F107" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45399</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F108" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45448</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" t="s">
+        <v>183</v>
+      </c>
+      <c r="E109" t="s">
+        <v>57</v>
+      </c>
+      <c r="F109" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45463</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C110" t="s">
+        <v>126</v>
+      </c>
+      <c r="D110" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45672</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E111" t="s">
+        <v>179</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45677</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E112" t="s">
+        <v>179</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45721</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45728</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E114" t="s">
+        <v>179</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45734</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E115" t="s">
+        <v>179</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45736</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C116" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" t="s">
         <v>184</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
-        <v>44650</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="E52" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>44652</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>44679</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="E54" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="7">
-        <v>44679</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
-        <v>44684</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="E56" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="7">
-        <v>44685</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
-        <v>44692</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="E58" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="7">
-        <v>44704</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="7">
-        <v>44704</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="7">
-        <v>44707</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
-        <v>44723</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="E62" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="7">
-        <v>44782</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="7">
-        <v>44805</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="E64" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="7">
-        <v>44808</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="E65" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="7">
-        <v>44812</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="7">
-        <v>44825</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="E67" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="7">
-        <v>44834</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="7">
-        <v>44846</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="7">
-        <v>44846</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="7">
-        <v>44862</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="7">
-        <v>44869</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="E72" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="7">
-        <v>44886</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="7">
-        <v>44908</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="7">
-        <v>44936</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="7">
-        <v>44945</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="7">
-        <v>44952</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="7">
-        <v>44965</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="E78" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="7">
-        <v>44966</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="E79" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="7">
-        <v>44967</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="E80" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="7">
-        <v>44995</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="E81" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="7">
-        <v>45000</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="E82" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="7">
-        <v>45006</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="7">
-        <v>45013</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="7">
-        <v>45014</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="E85" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="7">
-        <v>45041</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="7">
-        <v>45042</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="7">
-        <v>45056</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="7">
-        <v>45087</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="E89" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="7">
-        <v>45106</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="7">
-        <v>45114</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="7">
-        <v>45195</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="7">
-        <v>45209</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="7">
-        <v>45224</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="7">
-        <v>45231</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="E95" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="7">
-        <v>45244</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="7">
-        <v>45248</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="E97" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="7">
-        <v>45258</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="7">
-        <v>45272</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="7">
-        <v>45273</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="E100" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="7">
-        <v>45354</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="7">
-        <v>45371</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="7">
-        <v>45375</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="7">
-        <v>45375</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="7">
-        <v>45375</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="7">
-        <v>45366</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="E106" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="7">
-        <v>45363</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="E107" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="7">
-        <v>45399</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="7">
-        <v>45448</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="7">
-        <v>45463</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="7">
-        <v>45672</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E111" t="s">
-        <v>180</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="7">
-        <v>45677</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E112" t="s">
-        <v>180</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="7">
-        <v>45721</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="7">
-        <v>45728</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E114" t="s">
-        <v>180</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="7">
-        <v>45734</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E115" t="s">
-        <v>180</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="7">
-        <v>45736</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C116" t="s">
-        <v>167</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>185</v>
       </c>
       <c r="E116" t="s">
         <v>57</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="7">
+      <c r="A117" s="1">
         <v>45739</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E117" t="s">
-        <v>180</v>
-      </c>
-      <c r="F117" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="7">
+      <c r="A118" s="1">
         <v>45757</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E118" t="s">
-        <v>180</v>
-      </c>
-      <c r="F118" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" t="s">
+        <v>179</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C120" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="7">
-        <v>45748</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E119" t="s">
-        <v>180</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="7">
-        <v>45809</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>188</v>
+      </c>
+      <c r="E120" t="s">
         <v>169</v>
       </c>
-      <c r="D120" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="F120" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F120" s="5" t="s">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E121" t="s">
+        <v>179</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45833</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45835</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C123" t="s">
+        <v>172</v>
+      </c>
+      <c r="D123" t="s">
+        <v>172</v>
+      </c>
+      <c r="E123" t="s">
+        <v>173</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="7">
-        <v>45823</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E121" t="s">
-        <v>180</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="4">
-        <v>45833</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="7">
-        <v>45835</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C123" t="s">
-        <v>173</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E123" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45849</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E124" t="s">
+        <v>179</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45863</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45906</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E126" t="s">
+        <v>179</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45956</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E127" t="s">
+        <v>179</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F123" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="4">
-        <v>45849</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E124" t="s">
-        <v>180</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="4">
-        <v>45863</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="4">
-        <v>45906</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E126" t="s">
-        <v>180</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="4">
-        <v>45956</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E127" t="s">
-        <v>180</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="4">
+      <c r="A128" s="1">
         <v>45961</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E128" t="s">
-        <v>180</v>
-      </c>
-      <c r="F128" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="4">
+      <c r="A129" s="1">
         <v>45972</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E129" t="s">
-        <v>180</v>
-      </c>
-      <c r="F129" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="4">
+      <c r="A130" s="1">
         <v>45989</v>
       </c>
-      <c r="B130" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F130" s="5" t="s">
+      <c r="B130" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="4">
+      <c r="A131" s="1">
         <v>45989</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E131" t="s">
-        <v>180</v>
-      </c>
-      <c r="F131" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="4">
+      <c r="A132" s="1">
         <v>45994</v>
       </c>
-      <c r="B132" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F132" s="5" t="s">
+      <c r="B132" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="7">
+      <c r="A133" s="1">
         <v>46064</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F133" s="8" t="s">
+      <c r="B133" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F133" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="7">
+      <c r="A134" s="1">
         <v>46071</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>180</v>
-      </c>
-      <c r="F134" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F134" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="7">
+      <c r="A135" s="1">
         <v>46090</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
-      </c>
-      <c r="F135" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F135" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="7">
+      <c r="A136" s="1">
         <v>46099</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B136" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E136" t="s">
-        <v>180</v>
-      </c>
-      <c r="F136" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F136" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="7">
+      <c r="A137" s="1">
         <v>46100</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F137" s="8" t="s">
+      <c r="B137" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F137" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="7">
+      <c r="A138" s="1">
         <v>46103</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F138" s="8" t="s">
+      <c r="B138" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F138" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="7">
+      <c r="A139" s="1">
         <v>46108</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E139" t="s">
-        <v>180</v>
-      </c>
-      <c r="F139" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F139" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="7">
+      <c r="A140" s="1">
         <v>46160</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E140" t="s">
-        <v>180</v>
-      </c>
-      <c r="F140" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F140" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="7">
+      <c r="A141" s="1">
         <v>46163</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E141" t="s">
-        <v>180</v>
-      </c>
-      <c r="F141" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F141" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="7">
+      <c r="A142" s="1">
         <v>46178</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E142" t="s">
-        <v>180</v>
-      </c>
-      <c r="F142" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F142" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="7">
+      <c r="A143" s="1">
         <v>46191</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E143" t="s">
-        <v>180</v>
-      </c>
-      <c r="F143" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F143" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="7"/>
-      <c r="B144" s="9"/>
-      <c r="F144" s="8"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="8"/>
-      <c r="F145" s="8"/>
+      <c r="A144" s="1"/>
+      <c r="B144" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
